--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-11_User_Access_Maintenance/06_BIBS_Templates_BRD-11_Configuration_Inputs_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-11_User_Access_Maintenance/06_BIBS_Templates_BRD-11_Configuration_Inputs_v2.0.xlsx
@@ -1726,7 +1726,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="29" customHeight="1">
+    <row r="18" ht="16" customHeight="1">
       <c r="A18" s="9" t="n">
         <v>4</v>
       </c>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="82" customHeight="1">
+    <row r="23" ht="69" customHeight="1">
       <c r="A23" s="12" t="n">
         <v>1</v>
       </c>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="95" customHeight="1">
+    <row r="24" ht="69" customHeight="1">
       <c r="A24" s="17" t="n">
         <v>2</v>
       </c>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="82" customHeight="1">
+    <row r="25" ht="69" customHeight="1">
       <c r="A25" s="12" t="n">
         <v>3</v>
       </c>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="69" customHeight="1">
+    <row r="28" ht="56" customHeight="1">
       <c r="A28" s="17" t="n">
         <v>6</v>
       </c>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
     </row>
-    <row r="6" outlineLevel="1" ht="28" customHeight="1">
+    <row r="6" outlineLevel="1" ht="15.5" customHeight="1">
       <c r="A6" s="30" t="inlineStr">
         <is>
           <t>How it is loaded</t>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
     </row>
-    <row r="3" outlineLevel="1" ht="40.5" customHeight="1">
+    <row r="3" outlineLevel="1" ht="28" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
           <t>Purpose</t>
@@ -11788,7 +11788,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="18" customHeight="1">
       <c r="A17" s="47" t="inlineStr">
         <is>
           <t>Example – overwrite or delete</t>
@@ -18470,7 +18470,7 @@
         </is>
       </c>
     </row>
-    <row r="3" outlineLevel="1" ht="28" customHeight="1">
+    <row r="3" outlineLevel="1" ht="15.5" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
           <t>Purpose</t>
@@ -18506,7 +18506,7 @@
         </is>
       </c>
     </row>
-    <row r="6" outlineLevel="1" ht="40.5" customHeight="1">
+    <row r="6" outlineLevel="1" ht="28" customHeight="1">
       <c r="A6" s="30" t="inlineStr">
         <is>
           <t>How it is loaded</t>
@@ -23509,7 +23509,7 @@
         </is>
       </c>
     </row>
-    <row r="6" outlineLevel="1" ht="53" customHeight="1">
+    <row r="6" outlineLevel="1" ht="40.5" customHeight="1">
       <c r="A6" s="30" t="inlineStr">
         <is>
           <t>How it is loaded</t>
@@ -26937,7 +26937,7 @@
         </is>
       </c>
     </row>
-    <row r="3" outlineLevel="1" ht="28" customHeight="1">
+    <row r="3" outlineLevel="1" ht="15.5" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
           <t>Purpose</t>
@@ -30920,7 +30920,7 @@
       </c>
       <c r="E6" s="19" t="n"/>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7">
       <c r="A7" s="57" t="inlineStr">
         <is>
           <t>Bulk request action (UA_ACTION)</t>
@@ -30988,7 +30988,7 @@
       </c>
       <c r="E10" s="14" t="n"/>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11">
       <c r="A11" s="41" t="inlineStr">
         <is>
           <t>Privilege level (PRIVILEGE_LEVEL)</t>
@@ -31026,7 +31026,7 @@
       </c>
       <c r="E12" s="19" t="n"/>
     </row>
-    <row r="13" ht="28" customHeight="1">
+    <row r="13">
       <c r="A13" s="41" t="n"/>
       <c r="B13" s="19" t="n"/>
       <c r="C13" s="56" t="inlineStr">
@@ -31041,7 +31041,7 @@
       </c>
       <c r="E13" s="19" t="n"/>
     </row>
-    <row r="14" ht="28" customHeight="1">
+    <row r="14">
       <c r="A14" s="41" t="n"/>
       <c r="B14" s="19" t="n"/>
       <c r="C14" s="56" t="inlineStr">
@@ -31147,7 +31147,7 @@
       </c>
       <c r="E19" s="19" t="n"/>
     </row>
-    <row r="20" ht="28" customHeight="1">
+    <row r="20">
       <c r="A20" s="41" t="n"/>
       <c r="B20" s="19" t="n"/>
       <c r="C20" s="56" t="inlineStr">
@@ -31298,7 +31298,7 @@
       </c>
       <c r="E28" s="19" t="n"/>
     </row>
-    <row r="29" ht="28" customHeight="1">
+    <row r="29">
       <c r="A29" s="57" t="inlineStr">
         <is>
           <t>Review frequency (REVIEW_FREQUENCY)</t>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="E31" s="19" t="n"/>
     </row>
-    <row r="32" ht="40.5" customHeight="1">
+    <row r="32" ht="28" customHeight="1">
       <c r="A32" s="41" t="n"/>
       <c r="B32" s="19" t="n"/>
       <c r="C32" s="56" t="inlineStr">
@@ -31389,7 +31389,7 @@
       </c>
       <c r="E33" s="19" t="n"/>
     </row>
-    <row r="34" ht="40.5" customHeight="1">
+    <row r="34" ht="28" customHeight="1">
       <c r="A34" s="41" t="n"/>
       <c r="B34" s="19" t="n"/>
       <c r="C34" s="56" t="inlineStr">
@@ -31404,7 +31404,7 @@
       </c>
       <c r="E34" s="19" t="n"/>
     </row>
-    <row r="35" ht="53" customHeight="1">
+    <row r="35" ht="40.5" customHeight="1">
       <c r="A35" s="41" t="n"/>
       <c r="B35" s="19" t="n"/>
       <c r="C35" s="56" t="inlineStr">
@@ -31434,7 +31434,7 @@
       </c>
       <c r="E36" s="19" t="n"/>
     </row>
-    <row r="37" ht="40.5" customHeight="1">
+    <row r="37" ht="28" customHeight="1">
       <c r="A37" s="41" t="n"/>
       <c r="B37" s="19" t="n"/>
       <c r="C37" s="56" t="inlineStr">
@@ -31449,7 +31449,7 @@
       </c>
       <c r="E37" s="19" t="n"/>
     </row>
-    <row r="38" ht="28" customHeight="1">
+    <row r="38">
       <c r="A38" s="41" t="n"/>
       <c r="B38" s="19" t="n"/>
       <c r="C38" s="56" t="inlineStr">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="E42" s="19" t="n"/>
     </row>
-    <row r="43" ht="53" customHeight="1">
+    <row r="43" ht="40.5" customHeight="1">
       <c r="A43" s="41" t="n"/>
       <c r="B43" s="19" t="n"/>
       <c r="C43" s="56" t="inlineStr">
@@ -31554,7 +31554,7 @@
       </c>
       <c r="E44" s="19" t="n"/>
     </row>
-    <row r="45" ht="40.5" customHeight="1">
+    <row r="45" ht="28" customHeight="1">
       <c r="A45" s="41" t="n"/>
       <c r="B45" s="19" t="n"/>
       <c r="C45" s="56" t="inlineStr">
@@ -31569,7 +31569,7 @@
       </c>
       <c r="E45" s="19" t="n"/>
     </row>
-    <row r="46" ht="40.5" customHeight="1">
+    <row r="46" ht="28" customHeight="1">
       <c r="A46" s="41" t="n"/>
       <c r="B46" s="19" t="n"/>
       <c r="C46" s="56" t="inlineStr">
@@ -31682,7 +31682,7 @@
       <c r="D52" s="19" t="n"/>
       <c r="E52" s="19" t="n"/>
     </row>
-    <row r="53" ht="28" customHeight="1">
+    <row r="53">
       <c r="A53" s="41" t="n"/>
       <c r="B53" s="19" t="n"/>
       <c r="C53" s="56" t="inlineStr">
@@ -31737,7 +31737,7 @@
       <c r="D57" s="19" t="n"/>
       <c r="E57" s="19" t="n"/>
     </row>
-    <row r="58" ht="28" customHeight="1">
+    <row r="58">
       <c r="A58" s="57" t="inlineStr">
         <is>
           <t>Question status (QUESTION_STATUS)</t>
